--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,113 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129314701</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98676</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flartjärnberget, Flartjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561561</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7043064</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59997-2024 artfynd.xlsx
+++ b/artfynd/A 59997-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129314701</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
